--- a/gd/excel/Quest.xlsx
+++ b/gd/excel/Quest.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -600,6 +600,27 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>一个非常非常非常非常非常非常非常非常非常非常非常非常非常长的任务标题用来验证长文本预览</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>这段任务描述特别特别长：它用来验证翻译编辑器里长文本的两行截断预览、点击展开成完整 textarea、失焦收起回到预览，同时原文列也会随之展开便于对照翻译，请确认这一整套交互都正常工作、保存按钮始终垂直居中且与操作列表头对齐。</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>10</v>
       </c>
     </row>

--- a/gd/excel/Quest.xlsx
+++ b/gd/excel/Quest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
+      <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <color rgb="005D6B78"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -47,24 +41,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C9A227"/>
-        <bgColor rgb="00C9A227"/>
+        <fgColor rgb="001F3A5F"/>
+        <bgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C98A2E"/>
+        <bgColor rgb="00C98A2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
+        <fgColor rgb="00F3F6F8"/>
+        <bgColor rgb="00F3F6F8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -78,21 +72,52 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -101,16 +126,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EDF7EE"/>
-          <bgColor rgb="00EDF7EE"/>
+          <fgColor rgb="00F7FAFC"/>
+          <bgColor rgb="00F7FAFC"/>
         </patternFill>
       </fill>
       <border>
         <left style="thin">
-          <color rgb="00CCCCCC"/>
+          <color rgb="00D8E1E8"/>
         </left>
         <right style="thin">
-          <color rgb="00CCCCCC"/>
+          <color rgb="00D8E1E8"/>
         </right>
       </border>
     </dxf>
@@ -123,10 +148,10 @@
       </fill>
       <border>
         <left style="thin">
-          <color rgb="00CCCCCC"/>
+          <color rgb="00D8E1E8"/>
         </left>
         <right style="thin">
-          <color rgb="00CCCCCC"/>
+          <color rgb="00D8E1E8"/>
         </right>
       </border>
     </dxf>
@@ -489,10 +514,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F6F73"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -500,6 +526,9 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -512,19 +541,19 @@
       <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Title
-string[i18n]</t>
+string</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Description
-string[i18n]</t>
+string</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t>RewardItemId
-int32[ref:Item.Id]</t>
+int32</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -533,33 +562,48 @@
 int32</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Test
+vector&lt;double&gt;</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="6" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>任务唯一ID，禁止修改</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>任务标题（多语言）</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>任务描述（多语言）</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>奖励道具ID，关联 Item.Id</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>接取等级要求</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>测试测试</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -625,7 +669,11 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:E1000">
+  <mergeCells count="2">
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A3:H1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/gd/excel/Quest.xlsx
+++ b/gd/excel/Quest.xlsx
@@ -27,12 +27,11 @@
     </font>
     <font>
       <name val="Aptos"/>
-      <i val="1"/>
-      <color rgb="005D6B78"/>
+      <color rgb="00475569"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,24 +40,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3A5F"/>
-        <bgColor rgb="001F3A5F"/>
+        <fgColor rgb="00FBE6A5"/>
+        <bgColor rgb="00FBE6A5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C98A2E"/>
-        <bgColor rgb="00C98A2E"/>
+        <fgColor rgb="00DCE3EC"/>
+        <bgColor rgb="00DCE3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6F8"/>
-        <bgColor rgb="00F3F6F8"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7E6FA"/>
+        <bgColor rgb="00D7E6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7D9F7"/>
+        <bgColor rgb="00E7D9F7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -73,6 +84,143 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin"/>
@@ -81,7 +229,9 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
       <top style="thin"/>
       <bottom/>
       <diagonal/>
@@ -95,7 +245,9 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -104,58 +256,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F7FAFC"/>
-          <bgColor rgb="00F7FAFC"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00D8E1E8"/>
-        </left>
-        <right style="thin">
-          <color rgb="00D8E1E8"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00D8E1E8"/>
-        </left>
-        <right style="thin">
-          <color rgb="00D8E1E8"/>
-        </right>
-      </border>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -514,11 +660,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F6F73"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -531,156 +676,225 @@
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>任务唯一ID，禁止修改</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>任务标题（多语言）</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>任务描述（多语言）</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>奖励道具ID，关联 Item.Id</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>接取等级要求</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>测试测试000123</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="n"/>
+      <c r="H1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Id
 int32</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Title
 string</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Description
 string</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>RewardItemId
 int32</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>RequiredLevel
 int32</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>Test
-vector&lt;double&gt;</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="n"/>
-      <c r="H1" s="6" t="n"/>
+vector&lt;double&gt;[3]</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="17" t="n"/>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>任务唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>任务标题（多语言）</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>任务描述（多语言）</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>奖励道具ID，关联 Item.Id</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>接取等级要求</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>测试测试</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="6" t="n"/>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="19" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>数据项[1]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>数据项[2]</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>数据项[3]</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>新手冒险</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>完成你的第一次冒险</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>屠龙勇士</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>击败邪恶的巨龙</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10</v>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>#1
+double</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>#2
+double</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>#3
+double</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>一个非常非常非常非常非常非常非常非常非常非常非常非常非常长的任务标题用来验证长文本预览</t>
+          <t>新手冒险</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>这段任务描述特别特别长：它用来验证翻译编辑器里长文本的两行截断预览、点击展开成完整 textarea、失焦收起回到预览，同时原文列也会随之展开便于对照翻译，请确认这一整套交互都正常工作、保存按钮始终垂直居中且与操作列表头对齐。</t>
+          <t>完成你的第一次冒险</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>屠龙勇士</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>击败邪恶的巨龙</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>长标题</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>长描述</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:H1000">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="A5:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D5:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="引用" prompt="目标：Item.Id；最终以 canonical 校验为准" type="custom">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+    <dataValidation sqref="G5:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+    <dataValidation sqref="H5:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>